--- a/dataset-aromatique.xlsx
+++ b/dataset-aromatique.xlsx
@@ -1,15 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Azam\MTI\TESIS\new\fix\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1825A9E4-F330-41B1-B52E-164EC65241A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -3613,9 +3632,6 @@
     <t>Lady Million Fabulous — Rabanne</t>
   </si>
   <si>
-    <t>Tidak ditemukan nama resmi yang cocok di Fragrantica</t>
-  </si>
-  <si>
     <t>Vanilla Lace — Victoria’s Secret</t>
   </si>
   <si>
@@ -4820,13 +4836,16 @@
   </si>
   <si>
     <t>NO_REVOLUTIONIZE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vanilla Sundae Victoria's Secret </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4863,13 +4882,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4907,7 +4934,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -4941,6 +4968,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -4975,9 +5003,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5150,11 +5179,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H341"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="39.21875" customWidth="1"/>
+    <col min="3" max="3" width="30.6640625" customWidth="1"/>
+    <col min="4" max="4" width="35.109375" customWidth="1"/>
+    <col min="5" max="5" width="46.44140625" customWidth="1"/>
+    <col min="6" max="6" width="29.88671875" customWidth="1"/>
+    <col min="7" max="7" width="27.109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5180,7 +5217,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5197,16 +5234,16 @@
         <v>1010</v>
       </c>
       <c r="F2" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="G2" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H2" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5223,16 +5260,16 @@
         <v>1011</v>
       </c>
       <c r="F3" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="G3" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H3" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -5249,16 +5286,16 @@
         <v>1012</v>
       </c>
       <c r="F4" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="G4" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H4" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -5275,16 +5312,16 @@
         <v>1013</v>
       </c>
       <c r="F5" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="G5" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H5" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -5301,16 +5338,16 @@
         <v>1014</v>
       </c>
       <c r="F6" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="G6" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H6" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -5327,16 +5364,16 @@
         <v>1015</v>
       </c>
       <c r="F7" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="G7" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H7" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5353,16 +5390,16 @@
         <v>1016</v>
       </c>
       <c r="F8" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="G8" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H8" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -5379,16 +5416,16 @@
         <v>1017</v>
       </c>
       <c r="F9" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="G9" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H9" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -5405,16 +5442,16 @@
         <v>1018</v>
       </c>
       <c r="F10" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="G10" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H10" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -5431,16 +5468,16 @@
         <v>1019</v>
       </c>
       <c r="F11" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="G11" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H11" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -5457,16 +5494,16 @@
         <v>1020</v>
       </c>
       <c r="F12" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="G12" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="H12" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -5483,16 +5520,16 @@
         <v>1021</v>
       </c>
       <c r="F13" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="G13" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="H13" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -5509,16 +5546,16 @@
         <v>1022</v>
       </c>
       <c r="F14" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="G14" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="H14" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -5535,16 +5572,16 @@
         <v>1023</v>
       </c>
       <c r="F15" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="G15" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="H15" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -5561,16 +5598,16 @@
         <v>1024</v>
       </c>
       <c r="F16" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="G16" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="H16" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -5587,16 +5624,16 @@
         <v>1025</v>
       </c>
       <c r="F17" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="G17" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="H17" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -5613,16 +5650,16 @@
         <v>1026</v>
       </c>
       <c r="F18" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="G18" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="H18" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -5639,16 +5676,16 @@
         <v>1027</v>
       </c>
       <c r="F19" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="G19" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="H19" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -5665,16 +5702,16 @@
         <v>1028</v>
       </c>
       <c r="F20" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="G20" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="H20" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -5691,16 +5728,16 @@
         <v>1029</v>
       </c>
       <c r="F21" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="G21" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="H21" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -5717,16 +5754,16 @@
         <v>1030</v>
       </c>
       <c r="F22" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="G22" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="H22" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -5743,16 +5780,16 @@
         <v>1031</v>
       </c>
       <c r="F23" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="G23" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="H23" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -5769,16 +5806,16 @@
         <v>1032</v>
       </c>
       <c r="F24" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="G24" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="H24" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -5795,16 +5832,16 @@
         <v>1033</v>
       </c>
       <c r="F25" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="G25" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="H25" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -5818,16 +5855,16 @@
         <v>711</v>
       </c>
       <c r="F26" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="G26" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="H26" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5844,16 +5881,16 @@
         <v>1034</v>
       </c>
       <c r="F27" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="G27" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="H27" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -5870,16 +5907,16 @@
         <v>1035</v>
       </c>
       <c r="F28" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="G28" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="H28" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5896,16 +5933,16 @@
         <v>1036</v>
       </c>
       <c r="F29" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="G29" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H29" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5922,16 +5959,16 @@
         <v>1037</v>
       </c>
       <c r="F30" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="G30" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H30" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5945,16 +5982,16 @@
         <v>716</v>
       </c>
       <c r="F31" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="G31" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H31" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5971,16 +6008,16 @@
         <v>1038</v>
       </c>
       <c r="F32" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="G32" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H32" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5997,16 +6034,16 @@
         <v>1039</v>
       </c>
       <c r="F33" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="G33" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H33" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -6023,16 +6060,16 @@
         <v>1040</v>
       </c>
       <c r="F34" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="G34" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H34" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -6049,16 +6086,16 @@
         <v>1041</v>
       </c>
       <c r="F35" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="G35" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H35" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -6075,16 +6112,16 @@
         <v>1042</v>
       </c>
       <c r="F36" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="G36" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H36" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -6101,16 +6138,16 @@
         <v>1043</v>
       </c>
       <c r="F37" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="G37" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H37" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -6127,16 +6164,16 @@
         <v>1044</v>
       </c>
       <c r="F38" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="G38" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H38" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -6153,16 +6190,16 @@
         <v>1045</v>
       </c>
       <c r="F39" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="G39" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H39" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -6179,16 +6216,16 @@
         <v>1046</v>
       </c>
       <c r="F40" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="G40" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H40" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -6205,16 +6242,16 @@
         <v>1047</v>
       </c>
       <c r="F41" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="G41" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H41" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -6231,16 +6268,16 @@
         <v>1048</v>
       </c>
       <c r="F42" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="G42" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H42" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -6257,16 +6294,16 @@
         <v>1049</v>
       </c>
       <c r="F43" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="G43" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H43" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -6283,16 +6320,16 @@
         <v>1050</v>
       </c>
       <c r="F44" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="G44" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H44" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -6309,16 +6346,16 @@
         <v>1051</v>
       </c>
       <c r="F45" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="G45" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H45" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -6335,16 +6372,16 @@
         <v>1052</v>
       </c>
       <c r="F46" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="G46" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H46" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -6358,16 +6395,16 @@
         <v>732</v>
       </c>
       <c r="F47" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="G47" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H47" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -6384,16 +6421,16 @@
         <v>1053</v>
       </c>
       <c r="F48" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="G48" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H48" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -6410,16 +6447,16 @@
         <v>1054</v>
       </c>
       <c r="F49" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="G49" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H49" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -6436,16 +6473,16 @@
         <v>1055</v>
       </c>
       <c r="F50" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="G50" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H50" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -6462,16 +6499,16 @@
         <v>1056</v>
       </c>
       <c r="F51" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="G51" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H51" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -6488,16 +6525,16 @@
         <v>1057</v>
       </c>
       <c r="F52" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="G52" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H52" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -6514,16 +6551,16 @@
         <v>1058</v>
       </c>
       <c r="F53" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="G53" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H53" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -6540,16 +6577,16 @@
         <v>1059</v>
       </c>
       <c r="F54" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="G54" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H54" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -6566,16 +6603,16 @@
         <v>1060</v>
       </c>
       <c r="F55" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="G55" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H55" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -6592,16 +6629,16 @@
         <v>1061</v>
       </c>
       <c r="F56" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="G56" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H56" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -6618,16 +6655,16 @@
         <v>1062</v>
       </c>
       <c r="F57" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="G57" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H57" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -6644,16 +6681,16 @@
         <v>1063</v>
       </c>
       <c r="F58" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="G58" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H58" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -6670,16 +6707,16 @@
         <v>1064</v>
       </c>
       <c r="F59" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="G59" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H59" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -6696,16 +6733,16 @@
         <v>1064</v>
       </c>
       <c r="F60" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="G60" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H60" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
@@ -6722,16 +6759,16 @@
         <v>1065</v>
       </c>
       <c r="F61" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="G61" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H61" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
@@ -6748,16 +6785,16 @@
         <v>1066</v>
       </c>
       <c r="F62" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="G62" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H62" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
@@ -6774,16 +6811,16 @@
         <v>1067</v>
       </c>
       <c r="F63" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="G63" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H63" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
@@ -6800,16 +6837,16 @@
         <v>1068</v>
       </c>
       <c r="F64" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="G64" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H64" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
@@ -6826,16 +6863,16 @@
         <v>1069</v>
       </c>
       <c r="F65" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="G65" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H65" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
@@ -6852,16 +6889,16 @@
         <v>1070</v>
       </c>
       <c r="F66" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="G66" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H66" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
@@ -6875,16 +6912,16 @@
         <v>750</v>
       </c>
       <c r="F67" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="G67" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H67" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
@@ -6901,16 +6938,16 @@
         <v>1071</v>
       </c>
       <c r="F68" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="G68" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H68" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
@@ -6927,16 +6964,16 @@
         <v>1072</v>
       </c>
       <c r="F69" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="G69" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H69" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
@@ -6953,16 +6990,16 @@
         <v>1073</v>
       </c>
       <c r="F70" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="G70" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H70" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
@@ -6979,16 +7016,16 @@
         <v>1074</v>
       </c>
       <c r="F71" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="G71" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H71" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
@@ -7005,16 +7042,16 @@
         <v>1075</v>
       </c>
       <c r="F72" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="G72" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H72" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
@@ -7028,16 +7065,16 @@
         <v>756</v>
       </c>
       <c r="F73" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="G73" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H73" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
@@ -7054,16 +7091,16 @@
         <v>1076</v>
       </c>
       <c r="F74" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="G74" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H74" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
@@ -7077,16 +7114,16 @@
         <v>758</v>
       </c>
       <c r="F75" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="G75" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H75" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
@@ -7100,16 +7137,16 @@
         <v>759</v>
       </c>
       <c r="F76" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="G76" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H76" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
@@ -7123,16 +7160,16 @@
         <v>760</v>
       </c>
       <c r="F77" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="G77" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H77" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
@@ -7146,16 +7183,16 @@
         <v>761</v>
       </c>
       <c r="F78" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="G78" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H78" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
@@ -7172,16 +7209,16 @@
         <v>1077</v>
       </c>
       <c r="F79" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="G79" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H79" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
@@ -7198,16 +7235,16 @@
         <v>1078</v>
       </c>
       <c r="F80" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="G80" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H80" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
@@ -7224,16 +7261,16 @@
         <v>1079</v>
       </c>
       <c r="F81" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="G81" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H81" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
@@ -7247,16 +7284,16 @@
         <v>765</v>
       </c>
       <c r="F82" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="G82" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H82" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82</v>
       </c>
@@ -7270,16 +7307,16 @@
         <v>766</v>
       </c>
       <c r="F83" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="G83" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H83" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83</v>
       </c>
@@ -7293,16 +7330,16 @@
         <v>389</v>
       </c>
       <c r="F84" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="G84" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H84" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
@@ -7319,16 +7356,16 @@
         <v>1080</v>
       </c>
       <c r="F85" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="G85" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H85" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
@@ -7342,16 +7379,16 @@
         <v>768</v>
       </c>
       <c r="F86" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="G86" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H86" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
@@ -7368,16 +7405,16 @@
         <v>1081</v>
       </c>
       <c r="F87" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="G87" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H87" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87</v>
       </c>
@@ -7391,16 +7428,16 @@
         <v>770</v>
       </c>
       <c r="F88" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="G88" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H88" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88</v>
       </c>
@@ -7414,16 +7451,16 @@
         <v>771</v>
       </c>
       <c r="F89" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="G89" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H89" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
@@ -7437,16 +7474,16 @@
         <v>772</v>
       </c>
       <c r="F90" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="G90" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H90" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
@@ -7460,16 +7497,16 @@
         <v>773</v>
       </c>
       <c r="F91" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="G91" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H91" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>91</v>
       </c>
@@ -7486,16 +7523,16 @@
         <v>1082</v>
       </c>
       <c r="F92" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="G92" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H92" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
@@ -7509,16 +7546,16 @@
         <v>775</v>
       </c>
       <c r="F93" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="G93" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H93" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93</v>
       </c>
@@ -7535,16 +7572,16 @@
         <v>1083</v>
       </c>
       <c r="F94" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="G94" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H94" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94</v>
       </c>
@@ -7558,16 +7595,16 @@
         <v>777</v>
       </c>
       <c r="F95" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="G95" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H95" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95</v>
       </c>
@@ -7581,16 +7618,16 @@
         <v>778</v>
       </c>
       <c r="F96" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="G96" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H96" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
@@ -7607,16 +7644,16 @@
         <v>1084</v>
       </c>
       <c r="F97" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G97" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H97" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
@@ -7630,16 +7667,16 @@
         <v>780</v>
       </c>
       <c r="F98" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="G98" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H98" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98</v>
       </c>
@@ -7653,16 +7690,16 @@
         <v>781</v>
       </c>
       <c r="F99" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="G99" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H99" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99</v>
       </c>
@@ -7676,16 +7713,16 @@
         <v>782</v>
       </c>
       <c r="F100" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="G100" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H100" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>100</v>
       </c>
@@ -7702,16 +7739,16 @@
         <v>1085</v>
       </c>
       <c r="F101" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="G101" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H101" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>101</v>
       </c>
@@ -7725,16 +7762,16 @@
         <v>784</v>
       </c>
       <c r="F102" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="G102" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H102" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>102</v>
       </c>
@@ -7748,16 +7785,16 @@
         <v>785</v>
       </c>
       <c r="F103" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="G103" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H103" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>103</v>
       </c>
@@ -7771,16 +7808,16 @@
         <v>786</v>
       </c>
       <c r="F104" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="G104" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H104" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>104</v>
       </c>
@@ -7794,16 +7831,16 @@
         <v>787</v>
       </c>
       <c r="F105" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="G105" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H105" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>105</v>
       </c>
@@ -7817,16 +7854,16 @@
         <v>788</v>
       </c>
       <c r="F106" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="G106" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H106" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>106</v>
       </c>
@@ -7840,16 +7877,16 @@
         <v>789</v>
       </c>
       <c r="F107" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="G107" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H107" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>107</v>
       </c>
@@ -7866,16 +7903,16 @@
         <v>1086</v>
       </c>
       <c r="F108" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="G108" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H108" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>108</v>
       </c>
@@ -7889,16 +7926,16 @@
         <v>791</v>
       </c>
       <c r="F109" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="G109" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H109" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>109</v>
       </c>
@@ -7912,16 +7949,16 @@
         <v>792</v>
       </c>
       <c r="F110" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="G110" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H110" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>110</v>
       </c>
@@ -7935,16 +7972,16 @@
         <v>793</v>
       </c>
       <c r="F111" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="G111" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H111" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>111</v>
       </c>
@@ -7958,16 +7995,16 @@
         <v>794</v>
       </c>
       <c r="F112" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="G112" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H112" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>112</v>
       </c>
@@ -7981,16 +8018,16 @@
         <v>795</v>
       </c>
       <c r="F113" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="G113" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H113" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>113</v>
       </c>
@@ -8007,16 +8044,16 @@
         <v>1087</v>
       </c>
       <c r="F114" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="G114" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H114" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>114</v>
       </c>
@@ -8030,16 +8067,16 @@
         <v>797</v>
       </c>
       <c r="F115" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="G115" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H115" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>115</v>
       </c>
@@ -8053,16 +8090,16 @@
         <v>798</v>
       </c>
       <c r="F116" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="G116" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H116" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>116</v>
       </c>
@@ -8076,16 +8113,16 @@
         <v>799</v>
       </c>
       <c r="F117" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="G117" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H117" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>117</v>
       </c>
@@ -8099,16 +8136,16 @@
         <v>800</v>
       </c>
       <c r="F118" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="G118" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H118" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>118</v>
       </c>
@@ -8122,16 +8159,16 @@
         <v>801</v>
       </c>
       <c r="F119" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="G119" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H119" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>119</v>
       </c>
@@ -8145,16 +8182,16 @@
         <v>802</v>
       </c>
       <c r="F120" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="G120" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H120" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>120</v>
       </c>
@@ -8168,16 +8205,16 @@
         <v>803</v>
       </c>
       <c r="F121" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="G121" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H121" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>121</v>
       </c>
@@ -8191,16 +8228,16 @@
         <v>804</v>
       </c>
       <c r="F122" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="G122" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H122" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>122</v>
       </c>
@@ -8217,16 +8254,16 @@
         <v>1088</v>
       </c>
       <c r="F123" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="G123" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H123" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>123</v>
       </c>
@@ -8240,16 +8277,16 @@
         <v>806</v>
       </c>
       <c r="F124" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="G124" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H124" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>124</v>
       </c>
@@ -8263,16 +8300,16 @@
         <v>807</v>
       </c>
       <c r="F125" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="G125" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H125" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>125</v>
       </c>
@@ -8286,16 +8323,16 @@
         <v>808</v>
       </c>
       <c r="F126" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="G126" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H126" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>126</v>
       </c>
@@ -8309,16 +8346,16 @@
         <v>809</v>
       </c>
       <c r="F127" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="G127" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H127" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>127</v>
       </c>
@@ -8332,16 +8369,16 @@
         <v>810</v>
       </c>
       <c r="F128" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="G128" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H128" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>128</v>
       </c>
@@ -8358,16 +8395,16 @@
         <v>1089</v>
       </c>
       <c r="F129" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="G129" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H129" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>129</v>
       </c>
@@ -8381,16 +8418,16 @@
         <v>812</v>
       </c>
       <c r="F130" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="G130" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H130" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>130</v>
       </c>
@@ -8404,16 +8441,16 @@
         <v>813</v>
       </c>
       <c r="F131" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="G131" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H131" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>131</v>
       </c>
@@ -8427,16 +8464,16 @@
         <v>814</v>
       </c>
       <c r="F132" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="G132" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H132" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>132</v>
       </c>
@@ -8453,16 +8490,16 @@
         <v>1090</v>
       </c>
       <c r="F133" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="G133" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H133" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>133</v>
       </c>
@@ -8479,16 +8516,16 @@
         <v>1091</v>
       </c>
       <c r="F134" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="G134" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H134" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>134</v>
       </c>
@@ -8505,16 +8542,16 @@
         <v>1092</v>
       </c>
       <c r="F135" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="G135" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H135" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>135</v>
       </c>
@@ -8528,16 +8565,16 @@
         <v>818</v>
       </c>
       <c r="F136" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="G136" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H136" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>136</v>
       </c>
@@ -8551,16 +8588,16 @@
         <v>819</v>
       </c>
       <c r="F137" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="G137" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H137" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>137</v>
       </c>
@@ -8574,16 +8611,16 @@
         <v>820</v>
       </c>
       <c r="F138" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="G138" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H138" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>138</v>
       </c>
@@ -8597,16 +8634,16 @@
         <v>821</v>
       </c>
       <c r="F139" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="G139" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H139" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>139</v>
       </c>
@@ -8620,16 +8657,16 @@
         <v>822</v>
       </c>
       <c r="F140" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="G140" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H140" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>140</v>
       </c>
@@ -8643,16 +8680,16 @@
         <v>823</v>
       </c>
       <c r="F141" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="G141" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H141" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>141</v>
       </c>
@@ -8669,16 +8706,16 @@
         <v>1093</v>
       </c>
       <c r="F142" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="G142" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H142" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>142</v>
       </c>
@@ -8695,16 +8732,16 @@
         <v>1094</v>
       </c>
       <c r="F143" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="G143" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H143" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>143</v>
       </c>
@@ -8721,16 +8758,16 @@
         <v>1095</v>
       </c>
       <c r="F144" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="G144" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H144" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>144</v>
       </c>
@@ -8744,16 +8781,16 @@
         <v>827</v>
       </c>
       <c r="F145" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="G145" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H145" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>145</v>
       </c>
@@ -8770,16 +8807,16 @@
         <v>1096</v>
       </c>
       <c r="F146" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="G146" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H146" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>146</v>
       </c>
@@ -8793,16 +8830,16 @@
         <v>829</v>
       </c>
       <c r="F147" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="G147" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H147" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>147</v>
       </c>
@@ -8819,16 +8856,16 @@
         <v>1097</v>
       </c>
       <c r="F148" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="G148" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H148" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>148</v>
       </c>
@@ -8845,16 +8882,16 @@
         <v>1098</v>
       </c>
       <c r="F149" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="G149" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H149" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>149</v>
       </c>
@@ -8871,16 +8908,16 @@
         <v>1099</v>
       </c>
       <c r="F150" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="G150" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H150" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>150</v>
       </c>
@@ -8897,16 +8934,16 @@
         <v>1100</v>
       </c>
       <c r="F151" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="G151" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H151" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>151</v>
       </c>
@@ -8923,16 +8960,16 @@
         <v>1101</v>
       </c>
       <c r="F152" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="G152" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H152" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>152</v>
       </c>
@@ -8949,16 +8986,16 @@
         <v>1102</v>
       </c>
       <c r="F153" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="G153" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H153" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>153</v>
       </c>
@@ -8975,16 +9012,16 @@
         <v>1103</v>
       </c>
       <c r="F154" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="G154" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H154" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>154</v>
       </c>
@@ -9001,16 +9038,16 @@
         <v>1104</v>
       </c>
       <c r="F155" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="G155" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H155" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>155</v>
       </c>
@@ -9027,16 +9064,16 @@
         <v>1105</v>
       </c>
       <c r="F156" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="G156" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H156" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>156</v>
       </c>
@@ -9053,16 +9090,16 @@
         <v>1106</v>
       </c>
       <c r="F157" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="G157" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H157" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>157</v>
       </c>
@@ -9079,16 +9116,16 @@
         <v>1107</v>
       </c>
       <c r="F158" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="G158" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H158" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>158</v>
       </c>
@@ -9105,16 +9142,16 @@
         <v>1108</v>
       </c>
       <c r="F159" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="G159" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H159" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>159</v>
       </c>
@@ -9131,16 +9168,16 @@
         <v>1109</v>
       </c>
       <c r="F160" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="G160" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H160" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>160</v>
       </c>
@@ -9157,16 +9194,16 @@
         <v>1110</v>
       </c>
       <c r="F161" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="G161" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H161" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>161</v>
       </c>
@@ -9183,16 +9220,16 @@
         <v>1111</v>
       </c>
       <c r="F162" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="G162" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H162" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="163" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>162</v>
       </c>
@@ -9209,16 +9246,16 @@
         <v>1112</v>
       </c>
       <c r="F163" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="G163" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H163" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="164" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>163</v>
       </c>
@@ -9232,16 +9269,16 @@
         <v>844</v>
       </c>
       <c r="F164" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G164" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H164" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="165" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>164</v>
       </c>
@@ -9258,16 +9295,16 @@
         <v>1113</v>
       </c>
       <c r="F165" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="G165" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H165" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="166" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>165</v>
       </c>
@@ -9284,16 +9321,16 @@
         <v>1114</v>
       </c>
       <c r="F166" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="G166" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H166" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="167" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>166</v>
       </c>
@@ -9310,16 +9347,16 @@
         <v>1112</v>
       </c>
       <c r="F167" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="G167" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H167" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>167</v>
       </c>
@@ -9333,16 +9370,16 @@
         <v>847</v>
       </c>
       <c r="F168" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="G168" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H168" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>168</v>
       </c>
@@ -9356,16 +9393,16 @@
         <v>848</v>
       </c>
       <c r="F169" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="G169" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H169" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="170" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>169</v>
       </c>
@@ -9382,16 +9419,16 @@
         <v>1115</v>
       </c>
       <c r="F170" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="G170" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H170" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="171" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>170</v>
       </c>
@@ -9405,16 +9442,16 @@
         <v>850</v>
       </c>
       <c r="F171" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="G171" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H171" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="172" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>171</v>
       </c>
@@ -9431,16 +9468,16 @@
         <v>1116</v>
       </c>
       <c r="F172" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="G172" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H172" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="173" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>172</v>
       </c>
@@ -9457,16 +9494,16 @@
         <v>1117</v>
       </c>
       <c r="F173" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="G173" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H173" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="174" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>173</v>
       </c>
@@ -9480,16 +9517,16 @@
         <v>853</v>
       </c>
       <c r="F174" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="G174" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H174" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="175" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>174</v>
       </c>
@@ -9503,16 +9540,16 @@
         <v>854</v>
       </c>
       <c r="F175" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="G175" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H175" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="176" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>175</v>
       </c>
@@ -9529,16 +9566,16 @@
         <v>1118</v>
       </c>
       <c r="F176" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="G176" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H176" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="177" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>176</v>
       </c>
@@ -9552,16 +9589,16 @@
         <v>856</v>
       </c>
       <c r="F177" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="G177" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H177" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="178" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>177</v>
       </c>
@@ -9575,16 +9612,16 @@
         <v>857</v>
       </c>
       <c r="F178" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="G178" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H178" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="179" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>178</v>
       </c>
@@ -9598,16 +9635,16 @@
         <v>858</v>
       </c>
       <c r="F179" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="G179" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H179" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="180" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>179</v>
       </c>
@@ -9621,16 +9658,16 @@
         <v>859</v>
       </c>
       <c r="F180" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="G180" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H180" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="181" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>180</v>
       </c>
@@ -9647,16 +9684,16 @@
         <v>1119</v>
       </c>
       <c r="F181" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="G181" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H181" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="182" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>181</v>
       </c>
@@ -9673,16 +9710,16 @@
         <v>1120</v>
       </c>
       <c r="F182" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="G182" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H182" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="183" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>182</v>
       </c>
@@ -9696,16 +9733,16 @@
         <v>861</v>
       </c>
       <c r="F183" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="G183" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H183" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="184" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>183</v>
       </c>
@@ -9719,16 +9756,16 @@
         <v>862</v>
       </c>
       <c r="F184" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="G184" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H184" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="185" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>184</v>
       </c>
@@ -9745,16 +9782,16 @@
         <v>1121</v>
       </c>
       <c r="F185" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="G185" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H185" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="186" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>185</v>
       </c>
@@ -9771,16 +9808,16 @@
         <v>1122</v>
       </c>
       <c r="F186" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="G186" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H186" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="187" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>186</v>
       </c>
@@ -9794,16 +9831,16 @@
         <v>864</v>
       </c>
       <c r="F187" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="G187" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H187" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="188" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>187</v>
       </c>
@@ -9820,16 +9857,16 @@
         <v>1123</v>
       </c>
       <c r="F188" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="G188" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H188" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="189" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>188</v>
       </c>
@@ -9846,16 +9883,16 @@
         <v>1124</v>
       </c>
       <c r="F189" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="G189" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H189" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="190" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>189</v>
       </c>
@@ -9869,16 +9906,16 @@
         <v>536</v>
       </c>
       <c r="F190" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="G190" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H190" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="191" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>190</v>
       </c>
@@ -9892,16 +9929,16 @@
         <v>867</v>
       </c>
       <c r="F191" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="G191" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H191" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="192" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>191</v>
       </c>
@@ -9915,16 +9952,16 @@
         <v>868</v>
       </c>
       <c r="F192" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="G192" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H192" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="193" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>192</v>
       </c>
@@ -9941,16 +9978,16 @@
         <v>1125</v>
       </c>
       <c r="F193" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="G193" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H193" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="194" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>193</v>
       </c>
@@ -9964,16 +10001,16 @@
         <v>870</v>
       </c>
       <c r="F194" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="G194" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H194" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="195" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>194</v>
       </c>
@@ -9990,16 +10027,16 @@
         <v>1126</v>
       </c>
       <c r="F195" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="G195" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H195" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="196" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>195</v>
       </c>
@@ -10016,16 +10053,16 @@
         <v>1127</v>
       </c>
       <c r="F196" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="G196" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H196" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="197" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>196</v>
       </c>
@@ -10042,16 +10079,16 @@
         <v>1128</v>
       </c>
       <c r="F197" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="G197" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H197" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="198" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>197</v>
       </c>
@@ -10068,16 +10105,16 @@
         <v>1129</v>
       </c>
       <c r="F198" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="G198" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H198" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="199" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>198</v>
       </c>
@@ -10094,16 +10131,16 @@
         <v>1130</v>
       </c>
       <c r="F199" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="G199" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H199" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="200" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>199</v>
       </c>
@@ -10120,16 +10157,16 @@
         <v>1131</v>
       </c>
       <c r="F200" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="G200" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H200" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="201" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>200</v>
       </c>
@@ -10146,16 +10183,16 @@
         <v>1132</v>
       </c>
       <c r="F201" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="G201" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H201" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="202" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>201</v>
       </c>
@@ -10172,16 +10209,16 @@
         <v>1133</v>
       </c>
       <c r="F202" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="G202" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H202" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="203" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>202</v>
       </c>
@@ -10198,16 +10235,16 @@
         <v>1134</v>
       </c>
       <c r="F203" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="G203" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H203" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="204" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>203</v>
       </c>
@@ -10224,16 +10261,16 @@
         <v>1135</v>
       </c>
       <c r="F204" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="G204" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H204" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="205" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>204</v>
       </c>
@@ -10250,16 +10287,16 @@
         <v>1136</v>
       </c>
       <c r="F205" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="G205" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H205" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="206" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>205</v>
       </c>
@@ -10276,16 +10313,16 @@
         <v>1137</v>
       </c>
       <c r="F206" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="G206" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H206" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="207" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>206</v>
       </c>
@@ -10302,16 +10339,16 @@
         <v>1138</v>
       </c>
       <c r="F207" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="G207" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H207" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="208" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>207</v>
       </c>
@@ -10328,16 +10365,16 @@
         <v>1139</v>
       </c>
       <c r="F208" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="G208" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H208" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="209" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>208</v>
       </c>
@@ -10354,16 +10391,16 @@
         <v>1140</v>
       </c>
       <c r="F209" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="G209" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H209" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="210" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>209</v>
       </c>
@@ -10377,16 +10414,16 @@
         <v>885</v>
       </c>
       <c r="F210" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="G210" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H210" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="211" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>210</v>
       </c>
@@ -10403,16 +10440,16 @@
         <v>1141</v>
       </c>
       <c r="F211" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="G211" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H211" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="212" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>211</v>
       </c>
@@ -10429,16 +10466,16 @@
         <v>1142</v>
       </c>
       <c r="F212" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="G212" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H212" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="213" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>212</v>
       </c>
@@ -10455,16 +10492,16 @@
         <v>1143</v>
       </c>
       <c r="F213" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="G213" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H213" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="214" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>213</v>
       </c>
@@ -10481,16 +10518,16 @@
         <v>1144</v>
       </c>
       <c r="F214" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="G214" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H214" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="215" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>214</v>
       </c>
@@ -10507,16 +10544,16 @@
         <v>1145</v>
       </c>
       <c r="F215" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="G215" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H215" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="216" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>215</v>
       </c>
@@ -10533,16 +10570,16 @@
         <v>1146</v>
       </c>
       <c r="F216" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="G216" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H216" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="217" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>216</v>
       </c>
@@ -10559,16 +10596,16 @@
         <v>1147</v>
       </c>
       <c r="F217" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="G217" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H217" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="218" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>217</v>
       </c>
@@ -10585,16 +10622,16 @@
         <v>1148</v>
       </c>
       <c r="F218" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="G218" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H218" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="219" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>218</v>
       </c>
@@ -10611,16 +10648,16 @@
         <v>1149</v>
       </c>
       <c r="F219" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="G219" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H219" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="220" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>219</v>
       </c>
@@ -10637,16 +10674,16 @@
         <v>1150</v>
       </c>
       <c r="F220" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="G220" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H220" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="221" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>220</v>
       </c>
@@ -10663,16 +10700,16 @@
         <v>1151</v>
       </c>
       <c r="F221" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G221" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H221" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="222" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>221</v>
       </c>
@@ -10689,16 +10726,16 @@
         <v>1152</v>
       </c>
       <c r="F222" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="G222" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H222" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="223" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>222</v>
       </c>
@@ -10712,16 +10749,16 @@
         <v>898</v>
       </c>
       <c r="F223" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="G223" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H223" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="224" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>223</v>
       </c>
@@ -10738,16 +10775,16 @@
         <v>1153</v>
       </c>
       <c r="F224" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="G224" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H224" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="225" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>224</v>
       </c>
@@ -10764,16 +10801,16 @@
         <v>1154</v>
       </c>
       <c r="F225" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="G225" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H225" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="226" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>225</v>
       </c>
@@ -10790,16 +10827,16 @@
         <v>1155</v>
       </c>
       <c r="F226" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="G226" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H226" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="227" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>226</v>
       </c>
@@ -10816,16 +10853,16 @@
         <v>1156</v>
       </c>
       <c r="F227" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="G227" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H227" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="228" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>227</v>
       </c>
@@ -10842,16 +10879,16 @@
         <v>1157</v>
       </c>
       <c r="F228" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="G228" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H228" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="229" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>228</v>
       </c>
@@ -10868,16 +10905,16 @@
         <v>1158</v>
       </c>
       <c r="F229" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="G229" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H229" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="230" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>229</v>
       </c>
@@ -10894,16 +10931,16 @@
         <v>1159</v>
       </c>
       <c r="F230" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="G230" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H230" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="231" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>230</v>
       </c>
@@ -10920,16 +10957,16 @@
         <v>1160</v>
       </c>
       <c r="F231" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="G231" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H231" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="232" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>231</v>
       </c>
@@ -10946,16 +10983,16 @@
         <v>1161</v>
       </c>
       <c r="F232" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="G232" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H232" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="233" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>232</v>
       </c>
@@ -10972,16 +11009,16 @@
         <v>1162</v>
       </c>
       <c r="F233" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="G233" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H233" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="234" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>233</v>
       </c>
@@ -10998,16 +11035,16 @@
         <v>1163</v>
       </c>
       <c r="F234" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="G234" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H234" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="235" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>234</v>
       </c>
@@ -11024,16 +11061,16 @@
         <v>1164</v>
       </c>
       <c r="F235" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="G235" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H235" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="236" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>235</v>
       </c>
@@ -11050,16 +11087,16 @@
         <v>1165</v>
       </c>
       <c r="F236" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="G236" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H236" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="237" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>236</v>
       </c>
@@ -11076,16 +11113,16 @@
         <v>1166</v>
       </c>
       <c r="F237" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="G237" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H237" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="238" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>237</v>
       </c>
@@ -11102,16 +11139,16 @@
         <v>1167</v>
       </c>
       <c r="F238" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="G238" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H238" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="239" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>238</v>
       </c>
@@ -11128,16 +11165,16 @@
         <v>1168</v>
       </c>
       <c r="F239" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="G239" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H239" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="240" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>239</v>
       </c>
@@ -11154,16 +11191,16 @@
         <v>1169</v>
       </c>
       <c r="F240" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="G240" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H240" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="241" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>240</v>
       </c>
@@ -11180,16 +11217,16 @@
         <v>1170</v>
       </c>
       <c r="F241" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="G241" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H241" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="242" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>241</v>
       </c>
@@ -11206,16 +11243,16 @@
         <v>1171</v>
       </c>
       <c r="F242" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="G242" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H242" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="243" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>242</v>
       </c>
@@ -11229,16 +11266,16 @@
         <v>918</v>
       </c>
       <c r="F243" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="G243" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H243" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="244" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>243</v>
       </c>
@@ -11252,16 +11289,16 @@
         <v>919</v>
       </c>
       <c r="F244" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="G244" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H244" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="245" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>244</v>
       </c>
@@ -11278,16 +11315,16 @@
         <v>1172</v>
       </c>
       <c r="F245" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="G245" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H245" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="246" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>245</v>
       </c>
@@ -11301,16 +11338,16 @@
         <v>592</v>
       </c>
       <c r="F246" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="G246" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H246" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="247" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>246</v>
       </c>
@@ -11327,16 +11364,16 @@
         <v>1173</v>
       </c>
       <c r="F247" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="G247" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H247" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="248" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>247</v>
       </c>
@@ -11353,16 +11390,16 @@
         <v>1174</v>
       </c>
       <c r="F248" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="G248" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H248" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="249" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>248</v>
       </c>
@@ -11379,16 +11416,16 @@
         <v>1175</v>
       </c>
       <c r="F249" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="G249" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H249" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="250" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>249</v>
       </c>
@@ -11402,16 +11439,16 @@
         <v>924</v>
       </c>
       <c r="F250" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="G250" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H250" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="251" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>250</v>
       </c>
@@ -11428,16 +11465,16 @@
         <v>1176</v>
       </c>
       <c r="F251" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="G251" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H251" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="252" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>251</v>
       </c>
@@ -11454,16 +11491,16 @@
         <v>1177</v>
       </c>
       <c r="F252" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="G252" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H252" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="253" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>252</v>
       </c>
@@ -11480,16 +11517,16 @@
         <v>1178</v>
       </c>
       <c r="F253" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="G253" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H253" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="254" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>253</v>
       </c>
@@ -11506,16 +11543,16 @@
         <v>1179</v>
       </c>
       <c r="F254" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="G254" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H254" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="255" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>254</v>
       </c>
@@ -11532,16 +11569,16 @@
         <v>1180</v>
       </c>
       <c r="F255" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="G255" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H255" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="256" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>255</v>
       </c>
@@ -11558,16 +11595,16 @@
         <v>1181</v>
       </c>
       <c r="F256" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="G256" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H256" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="257" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>256</v>
       </c>
@@ -11584,16 +11621,16 @@
         <v>1182</v>
       </c>
       <c r="F257" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="G257" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H257" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="258" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>257</v>
       </c>
@@ -11610,16 +11647,16 @@
         <v>1183</v>
       </c>
       <c r="F258" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="G258" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H258" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="259" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>258</v>
       </c>
@@ -11636,16 +11673,16 @@
         <v>1184</v>
       </c>
       <c r="F259" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="G259" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H259" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="260" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>259</v>
       </c>
@@ -11662,16 +11699,16 @@
         <v>1185</v>
       </c>
       <c r="F260" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="G260" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H260" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="261" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>260</v>
       </c>
@@ -11685,16 +11722,16 @@
         <v>935</v>
       </c>
       <c r="F261" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="G261" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H261" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="262" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>261</v>
       </c>
@@ -11711,16 +11748,16 @@
         <v>1186</v>
       </c>
       <c r="F262" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="G262" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H262" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="263" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>262</v>
       </c>
@@ -11734,16 +11771,16 @@
         <v>937</v>
       </c>
       <c r="F263" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="G263" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H263" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="264" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>263</v>
       </c>
@@ -11757,16 +11794,16 @@
         <v>938</v>
       </c>
       <c r="F264" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="G264" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H264" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="265" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>264</v>
       </c>
@@ -11783,16 +11820,16 @@
         <v>1187</v>
       </c>
       <c r="F265" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="G265" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H265" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="266" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>265</v>
       </c>
@@ -11806,16 +11843,16 @@
         <v>940</v>
       </c>
       <c r="F266" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="G266" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H266" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="267" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>266</v>
       </c>
@@ -11832,16 +11869,16 @@
         <v>1188</v>
       </c>
       <c r="F267" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="G267" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H267" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="268" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>267</v>
       </c>
@@ -11858,16 +11895,16 @@
         <v>1189</v>
       </c>
       <c r="F268" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="G268" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H268" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="269" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>268</v>
       </c>
@@ -11884,16 +11921,16 @@
         <v>1190</v>
       </c>
       <c r="F269" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="G269" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H269" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="270" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>269</v>
       </c>
@@ -11910,16 +11947,16 @@
         <v>1191</v>
       </c>
       <c r="F270" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="G270" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H270" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="271" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>270</v>
       </c>
@@ -11936,16 +11973,16 @@
         <v>1192</v>
       </c>
       <c r="F271" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="G271" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H271" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="272" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>271</v>
       </c>
@@ -11962,16 +11999,16 @@
         <v>1193</v>
       </c>
       <c r="F272" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="G272" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H272" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="273" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>272</v>
       </c>
@@ -11985,16 +12022,16 @@
         <v>947</v>
       </c>
       <c r="F273" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="G273" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H273" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="274" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>273</v>
       </c>
@@ -12008,16 +12045,16 @@
         <v>948</v>
       </c>
       <c r="F274" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="G274" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H274" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="275" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>274</v>
       </c>
@@ -12034,16 +12071,16 @@
         <v>1194</v>
       </c>
       <c r="F275" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="G275" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H275" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="276" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>275</v>
       </c>
@@ -12060,16 +12097,16 @@
         <v>1195</v>
       </c>
       <c r="F276" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="G276" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H276" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="277" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>276</v>
       </c>
@@ -12086,16 +12123,16 @@
         <v>1196</v>
       </c>
       <c r="F277" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="G277" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H277" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="278" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>277</v>
       </c>
@@ -12112,16 +12149,16 @@
         <v>1197</v>
       </c>
       <c r="F278" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="G278" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H278" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="279" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>278</v>
       </c>
@@ -12138,16 +12175,16 @@
         <v>1198</v>
       </c>
       <c r="F279" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="G279" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H279" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="280" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>279</v>
       </c>
@@ -12161,19 +12198,19 @@
         <v>954</v>
       </c>
       <c r="E280" t="s">
-        <v>1199</v>
+        <v>1601</v>
       </c>
       <c r="F280" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="G280" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H280" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="281" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>280</v>
       </c>
@@ -12187,19 +12224,19 @@
         <v>627</v>
       </c>
       <c r="E281" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="F281" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="G281" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H281" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="282" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>281</v>
       </c>
@@ -12213,19 +12250,19 @@
         <v>955</v>
       </c>
       <c r="E282" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="F282" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="G282" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H282" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="283" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>282</v>
       </c>
@@ -12239,19 +12276,19 @@
         <v>956</v>
       </c>
       <c r="E283" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="F283" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="G283" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H283" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="284" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>283</v>
       </c>
@@ -12265,19 +12302,19 @@
         <v>630</v>
       </c>
       <c r="E284" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="F284" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="G284" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H284" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="285" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>284</v>
       </c>
@@ -12291,19 +12328,19 @@
         <v>957</v>
       </c>
       <c r="E285" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="F285" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="G285" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H285" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="286" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>285</v>
       </c>
@@ -12317,19 +12354,19 @@
         <v>958</v>
       </c>
       <c r="E286" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="F286" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="G286" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H286" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="287" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>286</v>
       </c>
@@ -12343,19 +12380,19 @@
         <v>959</v>
       </c>
       <c r="E287" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="F287" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="G287" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H287" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="288" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>287</v>
       </c>
@@ -12369,19 +12406,19 @@
         <v>709</v>
       </c>
       <c r="E288" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="F288" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="G288" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H288" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="289" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>288</v>
       </c>
@@ -12395,19 +12432,19 @@
         <v>960</v>
       </c>
       <c r="E289" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="F289" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="G289" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H289" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="290" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>289</v>
       </c>
@@ -12421,19 +12458,19 @@
         <v>961</v>
       </c>
       <c r="E290" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="F290" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="G290" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H290" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="291" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>290</v>
       </c>
@@ -12447,19 +12484,19 @@
         <v>297</v>
       </c>
       <c r="E291" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="F291" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G291" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H291" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="292" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>291</v>
       </c>
@@ -12473,19 +12510,19 @@
         <v>962</v>
       </c>
       <c r="E292" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="F292" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="G292" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H292" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="293" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>292</v>
       </c>
@@ -12499,19 +12536,19 @@
         <v>963</v>
       </c>
       <c r="E293" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F293" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="G293" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H293" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="294" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>293</v>
       </c>
@@ -12525,19 +12562,19 @@
         <v>964</v>
       </c>
       <c r="E294" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="F294" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="G294" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H294" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="295" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>294</v>
       </c>
@@ -12551,16 +12588,16 @@
         <v>965</v>
       </c>
       <c r="F295" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="G295" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H295" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="296" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>295</v>
       </c>
@@ -12574,16 +12611,16 @@
         <v>966</v>
       </c>
       <c r="F296" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="G296" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H296" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="297" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>296</v>
       </c>
@@ -12597,16 +12634,16 @@
         <v>967</v>
       </c>
       <c r="F297" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="G297" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H297" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="298" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>297</v>
       </c>
@@ -12620,16 +12657,16 @@
         <v>968</v>
       </c>
       <c r="F298" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="G298" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H298" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="299" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>298</v>
       </c>
@@ -12643,19 +12680,19 @@
         <v>969</v>
       </c>
       <c r="E299" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="F299" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="G299" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H299" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="300" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>299</v>
       </c>
@@ -12669,19 +12706,19 @@
         <v>970</v>
       </c>
       <c r="E300" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="F300" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="G300" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H300" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="301" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>300</v>
       </c>
@@ -12695,19 +12732,19 @@
         <v>971</v>
       </c>
       <c r="E301" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="F301" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="G301" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H301" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="302" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>301</v>
       </c>
@@ -12721,19 +12758,19 @@
         <v>972</v>
       </c>
       <c r="E302" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="F302" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="G302" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H302" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="303" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>302</v>
       </c>
@@ -12747,16 +12784,16 @@
         <v>973</v>
       </c>
       <c r="F303" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="G303" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H303" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="304" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>303</v>
       </c>
@@ -12770,19 +12807,19 @@
         <v>974</v>
       </c>
       <c r="E304" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="F304" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="G304" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H304" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="305" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>304</v>
       </c>
@@ -12796,19 +12833,19 @@
         <v>975</v>
       </c>
       <c r="E305" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="F305" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="G305" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H305" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="306" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>305</v>
       </c>
@@ -12822,16 +12859,16 @@
         <v>976</v>
       </c>
       <c r="F306" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="G306" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H306" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="307" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>306</v>
       </c>
@@ -12845,19 +12882,19 @@
         <v>977</v>
       </c>
       <c r="E307" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="F307" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="G307" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H307" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="308" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>307</v>
       </c>
@@ -12871,19 +12908,19 @@
         <v>978</v>
       </c>
       <c r="E308" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="F308" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="G308" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H308" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="309" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>308</v>
       </c>
@@ -12897,19 +12934,19 @@
         <v>979</v>
       </c>
       <c r="E309" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="F309" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="G309" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H309" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="310" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>309</v>
       </c>
@@ -12923,19 +12960,19 @@
         <v>980</v>
       </c>
       <c r="E310" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="F310" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="G310" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H310" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="311" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>310</v>
       </c>
@@ -12949,19 +12986,19 @@
         <v>981</v>
       </c>
       <c r="E311" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="F311" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="G311" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H311" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="312" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>311</v>
       </c>
@@ -12975,16 +13012,16 @@
         <v>982</v>
       </c>
       <c r="F312" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="G312" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H312" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="313" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>312</v>
       </c>
@@ -12998,19 +13035,19 @@
         <v>983</v>
       </c>
       <c r="E313" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F313" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="G313" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H313" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="314" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>313</v>
       </c>
@@ -13024,16 +13061,16 @@
         <v>984</v>
       </c>
       <c r="F314" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G314" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H314" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="315" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>314</v>
       </c>
@@ -13047,19 +13084,19 @@
         <v>985</v>
       </c>
       <c r="E315" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="F315" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G315" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H315" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="316" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>315</v>
       </c>
@@ -13073,19 +13110,19 @@
         <v>986</v>
       </c>
       <c r="E316" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="F316" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="G316" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H316" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="317" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>316</v>
       </c>
@@ -13099,19 +13136,19 @@
         <v>987</v>
       </c>
       <c r="E317" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="F317" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="G317" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H317" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="318" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>317</v>
       </c>
@@ -13125,19 +13162,19 @@
         <v>988</v>
       </c>
       <c r="E318" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="F318" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="G318" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H318" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="319" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>318</v>
       </c>
@@ -13151,19 +13188,19 @@
         <v>989</v>
       </c>
       <c r="E319" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="F319" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="G319" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H319" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="320" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>319</v>
       </c>
@@ -13177,19 +13214,19 @@
         <v>990</v>
       </c>
       <c r="E320" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="F320" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="G320" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H320" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="321" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>320</v>
       </c>
@@ -13203,19 +13240,19 @@
         <v>991</v>
       </c>
       <c r="E321" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="F321" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="G321" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H321" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="322" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>321</v>
       </c>
@@ -13229,19 +13266,19 @@
         <v>992</v>
       </c>
       <c r="E322" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="F322" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="G322" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H322" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="323" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>322</v>
       </c>
@@ -13255,19 +13292,19 @@
         <v>993</v>
       </c>
       <c r="E323" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="F323" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="G323" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H323" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="324" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>323</v>
       </c>
@@ -13281,19 +13318,19 @@
         <v>780</v>
       </c>
       <c r="E324" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="F324" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="G324" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H324" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="325" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>324</v>
       </c>
@@ -13307,19 +13344,19 @@
         <v>994</v>
       </c>
       <c r="E325" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="F325" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="G325" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H325" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="326" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>325</v>
       </c>
@@ -13333,19 +13370,19 @@
         <v>995</v>
       </c>
       <c r="E326" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="F326" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="G326" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H326" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="327" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>326</v>
       </c>
@@ -13359,19 +13396,19 @@
         <v>673</v>
       </c>
       <c r="E327" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="F327" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="G327" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H327" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="328" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>327</v>
       </c>
@@ -13385,19 +13422,19 @@
         <v>996</v>
       </c>
       <c r="E328" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="F328" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="G328" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H328" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="329" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>328</v>
       </c>
@@ -13411,19 +13448,19 @@
         <v>997</v>
       </c>
       <c r="E329" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F329" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="G329" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H329" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="330" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>329</v>
       </c>
@@ -13437,19 +13474,19 @@
         <v>998</v>
       </c>
       <c r="E330" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="F330" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="G330" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H330" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="331" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>330</v>
       </c>
@@ -13463,19 +13500,19 @@
         <v>999</v>
       </c>
       <c r="E331" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="F331" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="G331" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H331" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="332" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>331</v>
       </c>
@@ -13489,19 +13526,19 @@
         <v>1000</v>
       </c>
       <c r="E332" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F332" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="G332" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H332" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="333" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>332</v>
       </c>
@@ -13515,19 +13552,19 @@
         <v>1001</v>
       </c>
       <c r="E333" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F333" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="G333" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H333" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="334" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>333</v>
       </c>
@@ -13541,19 +13578,19 @@
         <v>1002</v>
       </c>
       <c r="E334" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="F334" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="G334" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H334" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="335" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>334</v>
       </c>
@@ -13567,19 +13604,19 @@
         <v>1003</v>
       </c>
       <c r="E335" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="F335" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="G335" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H335" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="336" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>335</v>
       </c>
@@ -13593,16 +13630,16 @@
         <v>1004</v>
       </c>
       <c r="F336" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="G336" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H336" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="337" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>336</v>
       </c>
@@ -13616,19 +13653,19 @@
         <v>1005</v>
       </c>
       <c r="E337" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="F337" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="G337" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H337" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="338" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>337</v>
       </c>
@@ -13642,16 +13679,16 @@
         <v>1006</v>
       </c>
       <c r="F338" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="G338" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H338" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="339" spans="1:8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>338</v>
       </c>
@@ -13665,19 +13702,19 @@
         <v>1007</v>
       </c>
       <c r="E339" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="F339" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="G339" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H339" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="340" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>339</v>
       </c>
@@ -13691,19 +13728,19 @@
         <v>1008</v>
       </c>
       <c r="E340" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="F340" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="G340" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H340" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="341" spans="1:8">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>340</v>
       </c>
@@ -13717,16 +13754,16 @@
         <v>1009</v>
       </c>
       <c r="E341" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="F341" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="G341" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H341" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
     </row>
   </sheetData>
